--- a/data/dividends_info_20260928.xlsx
+++ b/data/dividends_info_20260928.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>46.15000152587891</v>
+        <v>45.84000015258789</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1950162449063667</v>
+        <v>0.1963350778804897</v>
       </c>
       <c r="J2" t="n">
         <v>168</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.34999847412109</v>
+        <v>64.25</v>
       </c>
       <c r="I3" t="n">
-        <v>1.087801113595226</v>
+        <v>1.089494163424124</v>
       </c>
       <c r="J3" t="n">
         <v>147</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.960000038146973</v>
+        <v>9.039999961853027</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6696428542918696</v>
+        <v>0.6637168169600428</v>
       </c>
       <c r="J4" t="n">
         <v>77</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5049999952316284</v>
+        <v>0.5199999809265137</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7920792153998576</v>
+        <v>0.7692307974459868</v>
       </c>
       <c r="J5" t="n">
         <v>77</v>
@@ -710,12 +710,8 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>46.14500045776367</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.1950373802301218</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>77</v>
       </c>
@@ -758,10 +754,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.085000038146973</v>
+        <v>2.065000057220459</v>
       </c>
       <c r="I7" t="n">
-        <v>3.693045495981532</v>
+        <v>3.728813455997861</v>
       </c>
       <c r="J7" t="n">
         <v>56</v>
@@ -805,10 +801,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>24.72999954223633</v>
+        <v>24.57999992370605</v>
       </c>
       <c r="I8" t="n">
-        <v>1.091791366752221</v>
+        <v>1.098454031074263</v>
       </c>
       <c r="J8" t="n">
         <v>56</v>
@@ -852,10 +848,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.86000061035156</v>
+        <v>24.79999923706055</v>
       </c>
       <c r="I9" t="n">
-        <v>2.373290368119811</v>
+        <v>2.379032331252323</v>
       </c>
       <c r="J9" t="n">
         <v>56</v>
@@ -899,10 +895,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>13.03999996185303</v>
+        <v>13</v>
       </c>
       <c r="I10" t="n">
-        <v>1.610429452563881</v>
+        <v>1.615384615384615</v>
       </c>
       <c r="J10" t="n">
         <v>49</v>
@@ -946,10 +942,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5.949999809265137</v>
+        <v>5.889999866485596</v>
       </c>
       <c r="I11" t="n">
-        <v>3.36134464556733</v>
+        <v>3.395585815510971</v>
       </c>
       <c r="J11" t="n">
         <v>49</v>
@@ -993,10 +989,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>9.470000267028809</v>
+        <v>9.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6335797075835233</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="J12" t="n">
         <v>42</v>
@@ -1040,10 +1036,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>10.76000022888184</v>
+        <v>10.71000003814697</v>
       </c>
       <c r="I13" t="n">
-        <v>4.27509284586514</v>
+        <v>4.295051338576732</v>
       </c>
       <c r="J13" t="n">
         <v>28</v>
@@ -1087,10 +1083,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8.850000381469727</v>
+        <v>8.75</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6779660724719172</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="J14" t="n">
         <v>21</v>
@@ -1133,12 +1129,8 @@
           <t>IT0004587470</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>0.5049999952316284</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.7920792153998576</v>
-      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
         <v>21</v>
       </c>
@@ -1228,10 +1220,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>7.78000020980835</v>
+        <v>7.619999885559082</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4884318634348222</v>
+        <v>0.4986876715315321</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1274,12 +1266,8 @@
           <t>IT0003132476</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>24.72999954223633</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.091791366752221</v>
-      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>-7</v>
       </c>
@@ -1322,10 +1310,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.914000034332275</v>
+        <v>1.906000018119812</v>
       </c>
       <c r="I19" t="n">
-        <v>2.978056372913557</v>
+        <v>2.990556110079583</v>
       </c>
       <c r="J19" t="n">
         <v>-7</v>
@@ -1368,12 +1356,8 @@
           <t>NL0000226223</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>46.14500045776367</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.1950373802301218</v>
-      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>-7</v>
       </c>
@@ -1416,10 +1400,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>92</v>
+        <v>91.44999694824219</v>
       </c>
       <c r="I21" t="n">
-        <v>1.445652173913043</v>
+        <v>1.454346686039518</v>
       </c>
       <c r="J21" t="n">
         <v>-7</v>
@@ -1463,10 +1447,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5.920000076293945</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="I22" t="n">
-        <v>5.067567502259338</v>
+        <v>5.050505001853162</v>
       </c>
       <c r="J22" t="n">
         <v>-14</v>
@@ -1486,7 +1470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C213"/>
+  <dimension ref="A1:C233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2801,7 +2785,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2954,7 +2938,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3107,7 +3091,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3124,7 +3108,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ETI S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3141,7 +3125,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3158,7 +3142,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3175,7 +3159,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3192,7 +3176,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3209,7 +3193,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3226,7 +3210,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3243,7 +3227,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3253,14 +3237,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3277,7 +3261,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3294,7 +3278,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3304,14 +3288,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3328,7 +3312,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3345,7 +3329,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3362,7 +3346,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3379,7 +3363,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3396,7 +3380,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3413,7 +3397,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3430,7 +3414,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3447,7 +3431,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3457,14 +3441,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3481,7 +3465,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3498,7 +3482,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3515,7 +3499,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3532,7 +3516,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3549,7 +3533,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3566,7 +3550,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3583,7 +3567,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3600,7 +3584,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3617,7 +3601,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3634,7 +3618,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3651,7 +3635,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3668,7 +3652,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3685,7 +3669,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3702,7 +3686,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3719,7 +3703,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3736,7 +3720,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3753,7 +3737,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>OPT S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3770,7 +3754,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3780,14 +3764,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3804,7 +3788,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3821,7 +3805,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3838,7 +3822,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3855,7 +3839,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3872,7 +3856,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3889,7 +3873,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3899,14 +3883,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3923,7 +3907,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3933,14 +3917,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3957,7 +3941,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3974,7 +3958,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3984,14 +3968,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4008,7 +3992,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4025,7 +4009,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4042,7 +4026,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>First Point S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4059,7 +4043,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4076,7 +4060,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4093,7 +4077,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4110,7 +4094,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4127,7 +4111,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4137,14 +4121,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4154,14 +4138,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4178,7 +4162,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4195,7 +4179,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4212,7 +4196,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4229,7 +4213,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4246,7 +4230,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4263,7 +4247,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4273,7 +4257,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4349,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4382,7 +4366,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4450,7 +4434,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4460,14 +4444,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>LANDI RENZO S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4477,14 +4461,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4494,14 +4478,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>SB Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4511,14 +4495,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>SB Annual Report</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4528,14 +4512,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4545,14 +4529,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4562,19 +4546,19 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4586,46 +4570,46 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4637,46 +4621,46 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4688,12 +4672,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4705,97 +4689,97 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4807,12 +4791,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4824,29 +4808,29 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4858,29 +4842,29 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4892,12 +4876,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4909,12 +4893,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4926,12 +4910,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4943,63 +4927,63 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5011,12 +4995,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5028,12 +5012,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5045,12 +5029,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5062,29 +5046,29 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5096,17 +5080,357 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
+          <t>SOGEFI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
           <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>eVISO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>LANDI RENZO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>MAIRE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>eVISO S.p.A.</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>DIGITAL BROS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Ferretti S.p.A.</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>MAIRE S.p.A.</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>TECHNOGYM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>TECHNOGYM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
         <is>
           <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Stellantis N.V.</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Stellantis N.V.</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Prysmian S.p.A.</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Farmacosmo S.p.A.</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Davide Campari-Milano N.V.</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Davide Campari-Milano N.V.</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>DANIELI &amp; C. S.p.A.</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>A.B.P. Nocivelli S.p.A.</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CREACTIVES GROUP S.p.A.</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -5121,146 +5445,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DIGITAL BROS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0001469995</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>13.03999996185303</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1.610429452563881</v>
-      </c>
-      <c r="I2" t="n">
-        <v>49</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>eVISO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0005430936</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-11-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>9.470000267028809</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.6335797075835233</v>
-      </c>
-      <c r="I3" t="n">
-        <v>42</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5271,316 +5458,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CIRCLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Davide Campari-Milano N.V.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Davide Campari-Milano N.V.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Dipietro Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Energy S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>FOPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FOPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Farmacosmo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Stellantis N.V.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Stellantis N.V.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TECHNOGYM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TECHNOGYM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>